--- a/All_Insurers_2025_Databook.xlsx
+++ b/All_Insurers_2025_Databook.xlsx
@@ -1510,7 +1510,7 @@
         <v>70</v>
       </c>
       <c r="B102" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C102" t="s">
         <v>8</v>
@@ -2479,7 +2479,7 @@
         <v>36</v>
       </c>
       <c r="B60" t="n">
-        <v>0.0058</v>
+        <v>0.0265</v>
       </c>
       <c r="C60" t="s">
         <v>37</v>
@@ -2490,7 +2490,7 @@
         <v>38</v>
       </c>
       <c r="B61" t="n">
-        <v>0.0058</v>
+        <v>0.0305</v>
       </c>
       <c r="C61" t="s">
         <v>37</v>
@@ -2501,7 +2501,7 @@
         <v>39</v>
       </c>
       <c r="B62" t="n">
-        <v>0.0058</v>
+        <v>0.0343</v>
       </c>
       <c r="C62" t="s">
         <v>37</v>
@@ -2521,7 +2521,7 @@
         <v>41</v>
       </c>
       <c r="B64" t="n">
-        <v>0.0058</v>
+        <v>0.0378</v>
       </c>
       <c r="C64" t="s">
         <v>37</v>
@@ -2532,7 +2532,7 @@
         <v>42</v>
       </c>
       <c r="B65" t="n">
-        <v>0.0049</v>
+        <v>0.0368</v>
       </c>
       <c r="C65" t="s">
         <v>37</v>
@@ -2543,7 +2543,7 @@
         <v>43</v>
       </c>
       <c r="B66" t="n">
-        <v>0.0031</v>
+        <v>0.0349</v>
       </c>
       <c r="C66" t="s">
         <v>37</v>
@@ -2628,7 +2628,9 @@
       <c r="A80" t="s">
         <v>55</v>
       </c>
-      <c r="B80"/>
+      <c r="B80" t="n">
+        <v>4122</v>
+      </c>
       <c r="C80" t="s">
         <v>8</v>
       </c>
@@ -2637,7 +2639,9 @@
       <c r="A81" t="s">
         <v>56</v>
       </c>
-      <c r="B81"/>
+      <c r="B81" t="n">
+        <v>117</v>
+      </c>
       <c r="C81" t="s">
         <v>8</v>
       </c>
@@ -2646,7 +2650,9 @@
       <c r="A82" t="s">
         <v>57</v>
       </c>
-      <c r="B82"/>
+      <c r="B82" t="n">
+        <v>111</v>
+      </c>
       <c r="C82" t="s">
         <v>8</v>
       </c>
@@ -2655,7 +2661,9 @@
       <c r="A83" t="s">
         <v>58</v>
       </c>
-      <c r="B83"/>
+      <c r="B83" t="n">
+        <v>470</v>
+      </c>
       <c r="C83" t="s">
         <v>8</v>
       </c>
@@ -2664,7 +2672,9 @@
       <c r="A84" t="s">
         <v>59</v>
       </c>
-      <c r="B84"/>
+      <c r="B84" t="n">
+        <v>-266</v>
+      </c>
       <c r="C84" t="s">
         <v>8</v>
       </c>
@@ -2673,7 +2683,9 @@
       <c r="A85" t="s">
         <v>60</v>
       </c>
-      <c r="B85"/>
+      <c r="B85" t="n">
+        <v>14</v>
+      </c>
       <c r="C85" t="s">
         <v>8</v>
       </c>
@@ -2682,7 +2694,9 @@
       <c r="A86" t="s">
         <v>61</v>
       </c>
-      <c r="B86"/>
+      <c r="B86" t="n">
+        <v>4568</v>
+      </c>
       <c r="C86" t="s">
         <v>8</v>
       </c>
@@ -3111,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="B144" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="C144" t="s">
         <v>101</v>
@@ -3130,7 +3144,9 @@
       <c r="A146" t="s">
         <v>103</v>
       </c>
-      <c r="B146"/>
+      <c r="B146" t="n">
+        <v>5743</v>
+      </c>
       <c r="C146" t="s">
         <v>101</v>
       </c>
@@ -3139,7 +3155,9 @@
       <c r="A147" t="s">
         <v>104</v>
       </c>
-      <c r="B147"/>
+      <c r="B147" t="n">
+        <v>12618</v>
+      </c>
       <c r="C147" t="s">
         <v>101</v>
       </c>
@@ -3148,9 +3166,7 @@
       <c r="A148" t="s">
         <v>105</v>
       </c>
-      <c r="B148" t="n">
-        <v>1315</v>
-      </c>
+      <c r="B148"/>
       <c r="C148" t="s">
         <v>101</v>
       </c>
@@ -3516,7 +3532,9 @@
       <c r="A25" t="s">
         <v>10</v>
       </c>
-      <c r="B25"/>
+      <c r="B25" t="n">
+        <v>2696</v>
+      </c>
       <c r="C25" t="s">
         <v>12</v>
       </c>
@@ -3525,7 +3543,9 @@
       <c r="A26" t="s">
         <v>18</v>
       </c>
-      <c r="B26"/>
+      <c r="B26" t="n">
+        <v>140460</v>
+      </c>
       <c r="C26" t="s">
         <v>12</v>
       </c>
@@ -4463,7 +4483,9 @@
       <c r="A156" t="s">
         <v>111</v>
       </c>
-      <c r="B156"/>
+      <c r="B156" t="n">
+        <v>22374</v>
+      </c>
       <c r="C156" t="s">
         <v>108</v>
       </c>
@@ -4481,9 +4503,7 @@
       <c r="A158" t="s">
         <v>113</v>
       </c>
-      <c r="B158" t="n">
-        <v>-3030</v>
-      </c>
+      <c r="B158"/>
       <c r="C158" t="s">
         <v>108</v>
       </c>
@@ -4501,9 +4521,7 @@
       <c r="A160" t="s">
         <v>18</v>
       </c>
-      <c r="B160" t="n">
-        <v>196455</v>
-      </c>
+      <c r="B160"/>
       <c r="C160" t="s">
         <v>12</v>
       </c>
@@ -4550,7 +4568,9 @@
       <c r="A169" t="s">
         <v>118</v>
       </c>
-      <c r="B169"/>
+      <c r="B169" t="n">
+        <v>8787</v>
+      </c>
       <c r="C169" t="s">
         <v>119</v>
       </c>
@@ -4568,7 +4588,9 @@
       <c r="A171" t="s">
         <v>121</v>
       </c>
-      <c r="B171"/>
+      <c r="B171" t="n">
+        <v>4469</v>
+      </c>
       <c r="C171" t="s">
         <v>119</v>
       </c>
@@ -4595,7 +4617,9 @@
       <c r="A174" t="s">
         <v>18</v>
       </c>
-      <c r="B174"/>
+      <c r="B174" t="n">
+        <v>13256</v>
+      </c>
       <c r="C174" t="s">
         <v>12</v>
       </c>

--- a/All_Insurers_2025_Databook.xlsx
+++ b/All_Insurers_2025_Databook.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t xml:space="preserve">Mapping Financial Statements — Achmea</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t xml:space="preserve">30 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 years</t>
   </si>
   <si>
     <t xml:space="preserve">50 years</t>
@@ -919,9 +922,7 @@
       <c r="A24" t="s">
         <v>9</v>
       </c>
-      <c r="B24" t="n">
-        <v>9738</v>
-      </c>
+      <c r="B24"/>
       <c r="C24" t="s">
         <v>12</v>
       </c>
@@ -1148,35 +1149,33 @@
       <c r="A57" t="s">
         <v>43</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57"/>
+      <c r="C57" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" t="n">
         <v>0.03185</v>
       </c>
-      <c r="C57" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="s">
-        <v>44</v>
+      <c r="C58" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60" t="n">
-        <v>0.0233</v>
-      </c>
-      <c r="C60" t="s">
-        <v>37</v>
+      <c r="A60" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B61" t="n">
-        <v>0.0274</v>
+        <v>0.0233</v>
       </c>
       <c r="C61" t="s">
         <v>37</v>
@@ -1184,10 +1183,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B62" t="n">
-        <v>0.03135</v>
+        <v>0.0274</v>
       </c>
       <c r="C62" t="s">
         <v>37</v>
@@ -1195,10 +1194,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B63" t="n">
-        <v>0.0339</v>
+        <v>0.03135</v>
       </c>
       <c r="C63" t="s">
         <v>37</v>
@@ -1206,10 +1205,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B64" t="n">
-        <v>0.0347</v>
+        <v>0.0339</v>
       </c>
       <c r="C64" t="s">
         <v>37</v>
@@ -1217,10 +1216,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B65" t="n">
-        <v>0.03445</v>
+        <v>0.0347</v>
       </c>
       <c r="C65" t="s">
         <v>37</v>
@@ -1228,89 +1227,104 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0.03445</v>
+      </c>
+      <c r="C66" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
         <v>43</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B67"/>
+      <c r="C67" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" t="n">
         <v>0.0312</v>
       </c>
-      <c r="C66" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
+      <c r="C68" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B69" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="C69" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>47</v>
-      </c>
-      <c r="B70" t="n">
-        <v>30</v>
-      </c>
-      <c r="C70" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B71" t="n">
-        <v>0.045</v>
+        <v>0.023</v>
       </c>
       <c r="C71" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B72" t="n">
-        <v>0.721</v>
+        <v>30</v>
       </c>
       <c r="C72" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B73" t="n">
-        <v>0.861</v>
+        <v>0.045</v>
       </c>
       <c r="C73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>51</v>
+      </c>
+      <c r="B74" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="C74" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
         <v>52</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B75" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="C75" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>53</v>
+      </c>
+      <c r="B76" t="n">
         <v>0.551</v>
       </c>
-      <c r="C74" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="s">
-        <v>53</v>
+      <c r="C76" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="79">
@@ -1318,34 +1332,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="s">
+    <row r="81">
+      <c r="A81" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B80" t="n">
-        <v>1140</v>
-      </c>
-      <c r="C80" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>56</v>
-      </c>
-      <c r="B81" t="n">
-        <v>15</v>
-      </c>
-      <c r="C81" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B82" t="n">
-        <v>34</v>
+        <v>1140</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
@@ -1353,10 +1350,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B83" t="n">
-        <v>-160</v>
+        <v>15</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
@@ -1364,10 +1361,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B84" t="n">
-        <v>-76</v>
+        <v>34</v>
       </c>
       <c r="C84" t="s">
         <v>8</v>
@@ -1375,10 +1372,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B85" t="n">
-        <v>50</v>
+        <v>-160</v>
       </c>
       <c r="C85" t="s">
         <v>8</v>
@@ -1386,93 +1383,97 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>60</v>
+      </c>
+      <c r="B86" t="n">
+        <v>-82</v>
+      </c>
+      <c r="C86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
         <v>61</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B87" t="n">
+        <v>100</v>
+      </c>
+      <c r="C87" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>62</v>
+      </c>
+      <c r="B88" t="n">
         <v>1047</v>
       </c>
-      <c r="C86" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
+      <c r="C88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B89" t="n">
-        <v>108</v>
-      </c>
-      <c r="C89" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>64</v>
-      </c>
-      <c r="B90"/>
-      <c r="C90" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>65</v>
-      </c>
-      <c r="B91"/>
+        <v>64</v>
+      </c>
+      <c r="B91" t="n">
+        <v>108</v>
+      </c>
       <c r="C91" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>65</v>
+      </c>
+      <c r="B92" t="n">
+        <v>6</v>
+      </c>
+      <c r="C92" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
         <v>66</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B93" t="n">
+        <v>-6</v>
+      </c>
+      <c r="C93" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>67</v>
+      </c>
+      <c r="B94" t="n">
         <v>3</v>
       </c>
-      <c r="C92" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>63</v>
-      </c>
-      <c r="B95" t="n">
-        <v>1032</v>
-      </c>
-      <c r="C95" t="s">
+      <c r="C94" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s">
-        <v>64</v>
-      </c>
-      <c r="B96" t="n">
-        <v>15</v>
-      </c>
-      <c r="C96" t="s">
-        <v>8</v>
+      <c r="A96" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B97" t="n">
-        <v>-76</v>
+        <v>1032</v>
       </c>
       <c r="C97" t="s">
         <v>8</v>
@@ -1480,97 +1481,105 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>65</v>
+      </c>
+      <c r="B98" t="n">
+        <v>15</v>
+      </c>
+      <c r="C98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
         <v>66</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B99" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C99" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>67</v>
+      </c>
+      <c r="B100" t="n">
         <v>1044</v>
       </c>
-      <c r="C98" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
+      <c r="C100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B101" t="n">
-        <v>46</v>
-      </c>
-      <c r="C101" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>70</v>
-      </c>
-      <c r="B102" t="n">
-        <v>161</v>
-      </c>
-      <c r="C102" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>71</v>
-      </c>
-      <c r="B103"/>
+        <v>70</v>
+      </c>
+      <c r="B103" t="n">
+        <v>47</v>
+      </c>
       <c r="C103" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>72</v>
-      </c>
-      <c r="B104"/>
+        <v>71</v>
+      </c>
+      <c r="B104" t="n">
+        <v>164</v>
+      </c>
       <c r="C104" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
+        <v>72</v>
+      </c>
+      <c r="B105" t="n">
+        <v>306</v>
+      </c>
+      <c r="C105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
         <v>73</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B106" t="n">
+        <v>533</v>
+      </c>
+      <c r="C106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>74</v>
+      </c>
+      <c r="B107" t="n">
         <v>1051</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C107" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>55</v>
-      </c>
-      <c r="B109"/>
-      <c r="C109" t="s">
-        <v>8</v>
-      </c>
-    </row>
     <row r="110">
-      <c r="A110" t="s">
-        <v>56</v>
-      </c>
-      <c r="B110"/>
-      <c r="C110" t="s">
-        <v>8</v>
+      <c r="A110" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B111"/>
       <c r="C111" t="s">
@@ -1579,7 +1588,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B112"/>
       <c r="C112" t="s">
@@ -1588,7 +1597,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="B113"/>
       <c r="C113" t="s">
@@ -1597,7 +1606,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B114"/>
       <c r="C114" t="s">
@@ -1606,7 +1615,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B115"/>
       <c r="C115" t="s">
@@ -1615,7 +1624,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B116"/>
       <c r="C116" t="s">
@@ -1624,10 +1633,19 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B117"/>
       <c r="C117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>80</v>
+      </c>
+      <c r="B118"/>
+      <c r="C118" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1635,30 +1653,17 @@
       <c r="A119" t="s">
         <v>81</v>
       </c>
-      <c r="B119" t="n">
-        <v>122</v>
-      </c>
+      <c r="B119"/>
       <c r="C119" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>82</v>
-      </c>
-      <c r="B120" t="n">
-        <v>117</v>
-      </c>
-      <c r="C120" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B121" t="n">
-        <v>697</v>
+        <v>81</v>
       </c>
       <c r="C121" t="s">
         <v>8</v>
@@ -1666,74 +1671,76 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>83</v>
+      </c>
+      <c r="B122" t="n">
+        <v>77</v>
+      </c>
+      <c r="C122" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
         <v>84</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B123" t="n">
+        <v>697</v>
+      </c>
+      <c r="C123" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>85</v>
+      </c>
+      <c r="B124" t="n">
         <v>584</v>
       </c>
-      <c r="C122" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
+      <c r="C124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B126" t="n">
-        <v>318</v>
-      </c>
-      <c r="C126" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>87</v>
-      </c>
-      <c r="B127" t="n">
-        <v>143</v>
-      </c>
-      <c r="C127" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>88</v>
-      </c>
-      <c r="B128"/>
+        <v>87</v>
+      </c>
+      <c r="B128" t="n">
+        <v>318</v>
+      </c>
       <c r="C128" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>89</v>
-      </c>
-      <c r="B129"/>
+        <v>88</v>
+      </c>
+      <c r="B129" t="n">
+        <v>126</v>
+      </c>
       <c r="C129" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>90</v>
-      </c>
-      <c r="B130" t="n">
-        <v>2</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B130"/>
       <c r="C130" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B131"/>
       <c r="C131" t="s">
@@ -1742,12 +1749,19 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
+        <v>91</v>
+      </c>
+      <c r="B132"/>
+      <c r="C132" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
         <v>92</v>
       </c>
-      <c r="B132" t="n">
-        <v>447</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="B133"/>
+      <c r="C133" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1756,29 +1770,18 @@
         <v>93</v>
       </c>
       <c r="B134" t="n">
-        <v>79</v>
+        <v>447</v>
       </c>
       <c r="C134" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>94</v>
-      </c>
-      <c r="B135" t="n">
-        <v>86</v>
-      </c>
-      <c r="C135" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B136" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C136" t="s">
         <v>8</v>
@@ -1786,10 +1789,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B137" t="n">
-        <v>296</v>
+        <v>86</v>
       </c>
       <c r="C137" t="s">
         <v>8</v>
@@ -1797,10 +1800,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
+        <v>96</v>
+      </c>
+      <c r="B138" t="n">
         <v>97</v>
-      </c>
-      <c r="B138" t="n">
-        <v>142</v>
       </c>
       <c r="C138" t="s">
         <v>8</v>
@@ -1808,263 +1811,285 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
+        <v>97</v>
+      </c>
+      <c r="B139" t="n">
+        <v>296</v>
+      </c>
+      <c r="C139" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
         <v>98</v>
       </c>
-      <c r="B139" t="n">
+      <c r="B140" t="n">
+        <v>142</v>
+      </c>
+      <c r="C140" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>99</v>
+      </c>
+      <c r="B141" t="n">
         <v>65</v>
       </c>
-      <c r="C139" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="s">
-        <v>99</v>
+      <c r="C141" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s">
+      <c r="A144" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="B144" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="C144" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>102</v>
-      </c>
-      <c r="B145"/>
-      <c r="C145" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B146" t="n">
-        <v>5709</v>
+        <v>1.93</v>
       </c>
       <c r="C146" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>104</v>
-      </c>
-      <c r="B147" t="n">
-        <v>11013</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B147"/>
       <c r="C147" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
+        <v>104</v>
+      </c>
+      <c r="B148" t="n">
+        <v>5709</v>
+      </c>
+      <c r="C148" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
         <v>105</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B149" t="n">
+        <v>11013</v>
+      </c>
+      <c r="C149" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>106</v>
+      </c>
+      <c r="B150" t="n">
         <v>504</v>
       </c>
-      <c r="C148" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="s">
-        <v>106</v>
+      <c r="C150" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="s">
+      <c r="A153" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="B153" t="n">
-        <v>10596</v>
-      </c>
-      <c r="C153" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>109</v>
-      </c>
-      <c r="B154" t="n">
-        <v>10837</v>
-      </c>
-      <c r="C154" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B155" t="n">
-        <v>14205</v>
+        <v>10596</v>
       </c>
       <c r="C155" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B156" t="n">
-        <v>26763</v>
+        <v>10837</v>
       </c>
       <c r="C156" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B157" t="n">
-        <v>4967</v>
+        <v>14205</v>
       </c>
       <c r="C157" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B158" t="n">
-        <v>531</v>
+        <v>26763</v>
       </c>
       <c r="C158" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="B159" t="n">
-        <v>4969</v>
+        <v>4705</v>
       </c>
       <c r="C159" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="B160" t="n">
-        <v>77501</v>
+        <v>531</v>
       </c>
       <c r="C160" t="s">
-        <v>12</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>92</v>
+      </c>
+      <c r="B161" t="n">
+        <v>4969</v>
+      </c>
+      <c r="C161" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>114</v>
-      </c>
-      <c r="B162"/>
+        <v>18</v>
+      </c>
+      <c r="B162" t="n">
+        <v>77501</v>
+      </c>
       <c r="C162" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>115</v>
-      </c>
-      <c r="B163" t="n">
-        <v>59217</v>
-      </c>
-      <c r="C163" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
+        <v>115</v>
+      </c>
+      <c r="B164"/>
+      <c r="C164" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
         <v>116</v>
       </c>
-      <c r="B164" t="n">
+      <c r="B165" t="n">
+        <v>59217</v>
+      </c>
+      <c r="C165" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>117</v>
+      </c>
+      <c r="B166" t="n">
         <v>18284</v>
       </c>
-      <c r="C164" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="s">
-        <v>117</v>
+      <c r="C166" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="s">
+      <c r="A169" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B169"/>
-      <c r="C169" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>120</v>
-      </c>
-      <c r="B170" t="n">
-        <v>18542</v>
-      </c>
-      <c r="C170" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>121</v>
-      </c>
-      <c r="B171" t="n">
-        <v>4593</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="B171"/>
       <c r="C171" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B172" t="n">
-        <v>2170</v>
+        <v>18542</v>
       </c>
       <c r="C172" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B173" t="n">
-        <v>2179</v>
+        <v>4593</v>
       </c>
       <c r="C173" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
+        <v>123</v>
+      </c>
+      <c r="B174" t="n">
+        <v>2170</v>
+      </c>
+      <c r="C174" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>124</v>
+      </c>
+      <c r="B175" t="n">
+        <v>2179</v>
+      </c>
+      <c r="C175" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
         <v>18</v>
       </c>
-      <c r="B174" t="n">
+      <c r="B176" t="n">
         <v>27526</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C176" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2086,7 +2111,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2">
@@ -2096,7 +2121,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -2398,9 +2423,7 @@
       <c r="A51" t="s">
         <v>36</v>
       </c>
-      <c r="B51" t="n">
-        <v>0.0207</v>
-      </c>
+      <c r="B51"/>
       <c r="C51" t="s">
         <v>37</v>
       </c>
@@ -2409,9 +2432,7 @@
       <c r="A52" t="s">
         <v>38</v>
       </c>
-      <c r="B52" t="n">
-        <v>0.0247</v>
-      </c>
+      <c r="B52"/>
       <c r="C52" t="s">
         <v>37</v>
       </c>
@@ -2420,9 +2441,7 @@
       <c r="A53" t="s">
         <v>39</v>
       </c>
-      <c r="B53" t="n">
-        <v>0.0285</v>
-      </c>
+      <c r="B53"/>
       <c r="C53" t="s">
         <v>37</v>
       </c>
@@ -2440,9 +2459,7 @@
       <c r="A55" t="s">
         <v>41</v>
       </c>
-      <c r="B55" t="n">
-        <v>0.032</v>
-      </c>
+      <c r="B55"/>
       <c r="C55" t="s">
         <v>37</v>
       </c>
@@ -2451,9 +2468,7 @@
       <c r="A56" t="s">
         <v>42</v>
       </c>
-      <c r="B56" t="n">
-        <v>0.0319</v>
-      </c>
+      <c r="B56"/>
       <c r="C56" t="s">
         <v>37</v>
       </c>
@@ -2462,54 +2477,46 @@
       <c r="A57" t="s">
         <v>43</v>
       </c>
-      <c r="B57" t="n">
-        <v>0.0318</v>
-      </c>
+      <c r="B57"/>
       <c r="C57" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="s">
+    <row r="58">
+      <c r="A58" t="s">
         <v>44</v>
       </c>
+      <c r="B58"/>
+      <c r="C58" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60" t="n">
-        <v>0.0265</v>
-      </c>
-      <c r="C60" t="s">
-        <v>37</v>
+      <c r="A60" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" t="n">
-        <v>0.0305</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B61"/>
       <c r="C61" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" t="n">
-        <v>0.0343</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B62"/>
       <c r="C62" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B63"/>
       <c r="C63" t="s">
@@ -2518,105 +2525,112 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" t="n">
-        <v>0.0378</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B64"/>
       <c r="C64" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" t="n">
-        <v>0.0368</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B65"/>
       <c r="C65" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66"/>
+      <c r="C66" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
         <v>43</v>
       </c>
-      <c r="B66" t="n">
-        <v>0.0349</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="B67"/>
+      <c r="C67" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68"/>
+      <c r="C68" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B69" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="C69" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>47</v>
-      </c>
-      <c r="B70" t="n">
-        <v>20</v>
-      </c>
-      <c r="C70" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B71" t="n">
-        <v>0.06</v>
+        <v>0.032</v>
       </c>
       <c r="C71" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>50</v>
-      </c>
-      <c r="B72"/>
+        <v>48</v>
+      </c>
+      <c r="B72" t="n">
+        <v>20</v>
+      </c>
       <c r="C72" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>51</v>
-      </c>
-      <c r="B73"/>
+        <v>49</v>
+      </c>
+      <c r="B73" t="n">
+        <v>0.06</v>
+      </c>
       <c r="C73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B74"/>
       <c r="C74" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>52</v>
+      </c>
+      <c r="B75"/>
+      <c r="C75" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
         <v>53</v>
+      </c>
+      <c r="B76"/>
+      <c r="C76" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="79">
@@ -2624,34 +2638,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="s">
+    <row r="81">
+      <c r="A81" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B80" t="n">
-        <v>4122</v>
-      </c>
-      <c r="C80" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>56</v>
-      </c>
-      <c r="B81" t="n">
-        <v>117</v>
-      </c>
-      <c r="C81" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B82" t="n">
-        <v>111</v>
+        <v>4348</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
@@ -2659,10 +2656,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B83" t="n">
-        <v>470</v>
+        <v>191</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
@@ -2670,10 +2667,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B84" t="n">
-        <v>-266</v>
+        <v>120</v>
       </c>
       <c r="C84" t="s">
         <v>8</v>
@@ -2681,10 +2678,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B85" t="n">
-        <v>14</v>
+        <v>500</v>
       </c>
       <c r="C85" t="s">
         <v>8</v>
@@ -2692,123 +2689,143 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>60</v>
+      </c>
+      <c r="B86" t="n">
+        <v>-372</v>
+      </c>
+      <c r="C86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
         <v>61</v>
       </c>
-      <c r="B86" t="n">
-        <v>4568</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="B87" t="n">
+        <v>16</v>
+      </c>
+      <c r="C87" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="s">
+      <c r="A88" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
+      <c r="B88" t="n">
+        <v>4807</v>
+      </c>
+      <c r="C88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B89"/>
-      <c r="C89" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>64</v>
-      </c>
-      <c r="B90"/>
-      <c r="C90" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>65</v>
-      </c>
-      <c r="B91"/>
+        <v>64</v>
+      </c>
+      <c r="B91" t="n">
+        <v>226</v>
+      </c>
       <c r="C91" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>65</v>
+      </c>
+      <c r="B92" t="n">
+        <v>74</v>
+      </c>
+      <c r="C92" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
         <v>66</v>
       </c>
-      <c r="B92"/>
-      <c r="C92" t="s">
+      <c r="B93" t="n">
+        <v>-106</v>
+      </c>
+      <c r="C93" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="s">
+      <c r="A94" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>63</v>
-      </c>
-      <c r="B95"/>
-      <c r="C95" t="s">
+      <c r="B94" t="n">
+        <v>239</v>
+      </c>
+      <c r="C94" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s">
-        <v>64</v>
-      </c>
-      <c r="B96"/>
-      <c r="C96" t="s">
-        <v>8</v>
+      <c r="A96" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>65</v>
-      </c>
-      <c r="B97"/>
+        <v>64</v>
+      </c>
+      <c r="B97" t="n">
+        <v>4122</v>
+      </c>
       <c r="C97" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>65</v>
+      </c>
+      <c r="B98" t="n">
+        <v>117</v>
+      </c>
+      <c r="C98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
         <v>66</v>
       </c>
-      <c r="B98"/>
-      <c r="C98" t="s">
+      <c r="B99" t="n">
+        <v>-266</v>
+      </c>
+      <c r="C99" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
+      <c r="A100" t="s">
+        <v>67</v>
+      </c>
+      <c r="B100" t="n">
+        <v>4568</v>
+      </c>
+      <c r="C100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B101"/>
-      <c r="C101" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>70</v>
-      </c>
-      <c r="B102"/>
-      <c r="C102" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B103"/>
       <c r="C103" t="s">
@@ -2817,7 +2834,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B104"/>
       <c r="C104" t="s">
@@ -2826,46 +2843,42 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B105"/>
       <c r="C105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>73</v>
+      </c>
+      <c r="B106"/>
+      <c r="C106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>74</v>
+      </c>
+      <c r="B107"/>
+      <c r="C107" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>55</v>
-      </c>
-      <c r="B109" t="n">
-        <v>2209</v>
-      </c>
-      <c r="C109" t="s">
-        <v>8</v>
-      </c>
-    </row>
     <row r="110">
-      <c r="A110" t="s">
-        <v>56</v>
-      </c>
-      <c r="B110" t="n">
-        <v>146</v>
-      </c>
-      <c r="C110" t="s">
-        <v>8</v>
+      <c r="A110" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B111" t="n">
-        <v>-85</v>
+        <v>2209</v>
       </c>
       <c r="C111" t="s">
         <v>8</v>
@@ -2873,10 +2886,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B112" t="n">
-        <v>-302</v>
+        <v>146</v>
       </c>
       <c r="C112" t="s">
         <v>8</v>
@@ -2884,10 +2897,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="B113" t="n">
-        <v>-75</v>
+        <v>-84</v>
       </c>
       <c r="C113" t="s">
         <v>8</v>
@@ -2895,10 +2908,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B114" t="n">
-        <v>-23</v>
+        <v>-302</v>
       </c>
       <c r="C114" t="s">
         <v>8</v>
@@ -2906,10 +2919,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B115" t="n">
-        <v>-153</v>
+        <v>-75</v>
       </c>
       <c r="C115" t="s">
         <v>8</v>
@@ -2917,10 +2930,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="C116" t="s">
         <v>8</v>
@@ -2928,12 +2941,21 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
+        <v>79</v>
+      </c>
+      <c r="B117" t="n">
+        <v>-153</v>
+      </c>
+      <c r="C117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
         <v>80</v>
       </c>
-      <c r="B117" t="n">
-        <v>1734</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="B118"/>
+      <c r="C118" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2942,29 +2964,18 @@
         <v>81</v>
       </c>
       <c r="B119" t="n">
-        <v>215</v>
+        <v>1734</v>
       </c>
       <c r="C119" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>82</v>
-      </c>
-      <c r="B120" t="n">
-        <v>232</v>
-      </c>
-      <c r="C120" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B121" t="n">
-        <v>1994</v>
+        <v>215</v>
       </c>
       <c r="C121" t="s">
         <v>8</v>
@@ -2972,52 +2983,56 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>83</v>
+      </c>
+      <c r="B122" t="n">
+        <v>232</v>
+      </c>
+      <c r="C122" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
         <v>84</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B123" t="n">
+        <v>1994</v>
+      </c>
+      <c r="C123" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>85</v>
+      </c>
+      <c r="B124" t="n">
         <v>1502</v>
       </c>
-      <c r="C122" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
+      <c r="C124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B126" t="n">
-        <v>223</v>
-      </c>
-      <c r="C126" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>87</v>
-      </c>
-      <c r="B127"/>
-      <c r="C127" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>88</v>
-      </c>
-      <c r="B128"/>
+        <v>87</v>
+      </c>
+      <c r="B128" t="n">
+        <v>223</v>
+      </c>
       <c r="C128" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B129"/>
       <c r="C129" t="s">
@@ -3026,7 +3041,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B130"/>
       <c r="C130" t="s">
@@ -3035,7 +3050,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B131"/>
       <c r="C131" t="s">
@@ -3044,12 +3059,23 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
+        <v>91</v>
+      </c>
+      <c r="B132" t="n">
+        <v>3</v>
+      </c>
+      <c r="C132" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
         <v>92</v>
       </c>
-      <c r="B132" t="n">
-        <v>195</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="B133" t="n">
+        <v>6</v>
+      </c>
+      <c r="C133" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3058,29 +3084,18 @@
         <v>93</v>
       </c>
       <c r="B134" t="n">
-        <v>25</v>
+        <v>195</v>
       </c>
       <c r="C134" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>94</v>
-      </c>
-      <c r="B135" t="n">
-        <v>44</v>
-      </c>
-      <c r="C135" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B136" t="n">
-        <v>198</v>
+        <v>25</v>
       </c>
       <c r="C136" t="s">
         <v>8</v>
@@ -3088,10 +3103,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B137" t="n">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="C137" t="s">
         <v>8</v>
@@ -3099,262 +3114,284 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>97</v>
-      </c>
-      <c r="B138"/>
+        <v>96</v>
+      </c>
+      <c r="B138" t="n">
+        <v>198</v>
+      </c>
       <c r="C138" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
+        <v>97</v>
+      </c>
+      <c r="B139" t="n">
+        <v>151</v>
+      </c>
+      <c r="C139" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
         <v>98</v>
       </c>
-      <c r="B139"/>
-      <c r="C139" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="s">
+      <c r="B140"/>
+      <c r="C140" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
         <v>99</v>
       </c>
+      <c r="B141"/>
+      <c r="C141" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" t="s">
+      <c r="A144" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="B144" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C144" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>102</v>
-      </c>
-      <c r="B145"/>
-      <c r="C145" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B146" t="n">
-        <v>5743</v>
+        <v>2.2</v>
       </c>
       <c r="C146" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>104</v>
-      </c>
-      <c r="B147" t="n">
-        <v>12618</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B147"/>
       <c r="C147" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
+        <v>104</v>
+      </c>
+      <c r="B148" t="n">
+        <v>5743</v>
+      </c>
+      <c r="C148" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
         <v>105</v>
       </c>
-      <c r="B148"/>
-      <c r="C148" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="s">
+      <c r="B149" t="n">
+        <v>12618</v>
+      </c>
+      <c r="C149" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
         <v>106</v>
       </c>
+      <c r="B150"/>
+      <c r="C150" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" t="s">
+      <c r="A153" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="B153" t="n">
-        <v>913</v>
-      </c>
-      <c r="C153" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>109</v>
-      </c>
-      <c r="B154" t="n">
-        <v>16263</v>
-      </c>
-      <c r="C154" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B155" t="n">
-        <v>10696</v>
+        <v>913</v>
       </c>
       <c r="C155" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B156" t="n">
-        <v>24821</v>
+        <v>16263</v>
       </c>
       <c r="C156" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>112</v>
-      </c>
-      <c r="B157"/>
+        <v>111</v>
+      </c>
+      <c r="B157" t="n">
+        <v>10696</v>
+      </c>
       <c r="C157" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B158" t="n">
-        <v>452</v>
+        <v>24821</v>
       </c>
       <c r="C158" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="B159"/>
       <c r="C159" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="B160" t="n">
-        <v>79141</v>
+        <v>452</v>
       </c>
       <c r="C160" t="s">
-        <v>12</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>92</v>
+      </c>
+      <c r="B161"/>
+      <c r="C161" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>114</v>
+        <v>18</v>
       </c>
       <c r="B162" t="n">
-        <v>2638</v>
+        <v>79141</v>
       </c>
       <c r="C162" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>115</v>
-      </c>
-      <c r="B163" t="n">
-        <v>73966</v>
-      </c>
-      <c r="C163" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
+        <v>115</v>
+      </c>
+      <c r="B164" t="n">
+        <v>2638</v>
+      </c>
+      <c r="C164" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
         <v>116</v>
       </c>
-      <c r="B164" t="n">
+      <c r="B165" t="n">
+        <v>73966</v>
+      </c>
+      <c r="C165" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>117</v>
+      </c>
+      <c r="B166" t="n">
         <v>2537</v>
       </c>
-      <c r="C164" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="s">
-        <v>117</v>
+      <c r="C166" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="s">
+      <c r="A169" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B169" t="n">
-        <v>4641</v>
-      </c>
-      <c r="C169" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>120</v>
-      </c>
-      <c r="B170"/>
-      <c r="C170" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B171" t="n">
-        <v>5937</v>
+        <v>4641</v>
       </c>
       <c r="C171" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B172"/>
       <c r="C172" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>123</v>
-      </c>
-      <c r="B173"/>
+        <v>122</v>
+      </c>
+      <c r="B173" t="n">
+        <v>5937</v>
+      </c>
       <c r="C173" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
+        <v>123</v>
+      </c>
+      <c r="B174"/>
+      <c r="C174" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>124</v>
+      </c>
+      <c r="B175"/>
+      <c r="C175" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
         <v>18</v>
       </c>
-      <c r="B174" t="n">
+      <c r="B176" t="n">
         <v>10324</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C176" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3376,7 +3413,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2">
@@ -3386,7 +3423,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -3409,7 +3446,9 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7"/>
+      <c r="B7" t="n">
+        <v>92835</v>
+      </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
@@ -3418,7 +3457,9 @@
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8"/>
+      <c r="B8" t="n">
+        <v>40805</v>
+      </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
@@ -3427,7 +3468,9 @@
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
@@ -3436,7 +3479,9 @@
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10"/>
+      <c r="B10" t="n">
+        <v>133640</v>
+      </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
@@ -3450,7 +3495,9 @@
       <c r="A13" t="s">
         <v>7</v>
       </c>
-      <c r="B13"/>
+      <c r="B13" t="n">
+        <v>4124</v>
+      </c>
       <c r="C13" t="s">
         <v>8</v>
       </c>
@@ -3459,7 +3506,9 @@
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14"/>
+      <c r="B14" t="n">
+        <v>2696</v>
+      </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
@@ -3468,7 +3517,9 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15"/>
+      <c r="B15" t="n">
+        <v>6820</v>
+      </c>
       <c r="C15" t="s">
         <v>12</v>
       </c>
@@ -3514,7 +3565,9 @@
       <c r="A23" t="s">
         <v>7</v>
       </c>
-      <c r="B23"/>
+      <c r="B23" t="n">
+        <v>96959</v>
+      </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
@@ -3523,7 +3576,9 @@
       <c r="A24" t="s">
         <v>9</v>
       </c>
-      <c r="B24"/>
+      <c r="B24" t="n">
+        <v>40805</v>
+      </c>
       <c r="C24" t="s">
         <v>12</v>
       </c>
@@ -3688,7 +3743,9 @@
       <c r="A51" t="s">
         <v>36</v>
       </c>
-      <c r="B51"/>
+      <c r="B51" t="n">
+        <v>0.027</v>
+      </c>
       <c r="C51" t="s">
         <v>37</v>
       </c>
@@ -3697,7 +3754,9 @@
       <c r="A52" t="s">
         <v>38</v>
       </c>
-      <c r="B52"/>
+      <c r="B52" t="n">
+        <v>0.031</v>
+      </c>
       <c r="C52" t="s">
         <v>37</v>
       </c>
@@ -3706,7 +3765,9 @@
       <c r="A53" t="s">
         <v>39</v>
       </c>
-      <c r="B53"/>
+      <c r="B53" t="n">
+        <v>0.035</v>
+      </c>
       <c r="C53" t="s">
         <v>37</v>
       </c>
@@ -3724,7 +3785,9 @@
       <c r="A55" t="s">
         <v>41</v>
       </c>
-      <c r="B55"/>
+      <c r="B55" t="n">
+        <v>0.038</v>
+      </c>
       <c r="C55" t="s">
         <v>37</v>
       </c>
@@ -3733,7 +3796,9 @@
       <c r="A56" t="s">
         <v>42</v>
       </c>
-      <c r="B56"/>
+      <c r="B56" t="n">
+        <v>0.038</v>
+      </c>
       <c r="C56" t="s">
         <v>37</v>
       </c>
@@ -3742,55 +3807,63 @@
       <c r="A57" t="s">
         <v>43</v>
       </c>
-      <c r="B57"/>
+      <c r="B57" t="n">
+        <v>0.037</v>
+      </c>
       <c r="C57" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="s">
+    <row r="58">
+      <c r="A58" t="s">
         <v>44</v>
       </c>
+      <c r="B58"/>
+      <c r="C58" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60"/>
-      <c r="C60" t="s">
-        <v>37</v>
+      <c r="A60" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61"/>
+        <v>36</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0.022</v>
+      </c>
       <c r="C61" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62"/>
+        <v>38</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0.025</v>
+      </c>
       <c r="C62" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63"/>
+        <v>39</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0.029</v>
+      </c>
       <c r="C63" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B64"/>
       <c r="C64" t="s">
@@ -3799,94 +3872,113 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65"/>
+        <v>41</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0.033</v>
+      </c>
       <c r="C65" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="C66" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
         <v>43</v>
       </c>
-      <c r="B66"/>
-      <c r="C66" t="s">
+      <c r="B67" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="C67" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68"/>
+      <c r="C68" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B69" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="C69" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>47</v>
-      </c>
-      <c r="B70" t="n">
-        <v>30</v>
-      </c>
-      <c r="C70" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B71" t="n">
-        <v>0.04</v>
+        <v>0.032</v>
       </c>
       <c r="C71" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B72" t="n">
-        <v>0.67</v>
+        <v>30</v>
       </c>
       <c r="C72" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B73" t="n">
-        <v>0.86</v>
+        <v>0.04</v>
       </c>
       <c r="C73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>51</v>
+      </c>
+      <c r="B74" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="C74" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
         <v>52</v>
       </c>
-      <c r="B74"/>
-      <c r="C74" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="s">
+      <c r="B75" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C75" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
         <v>53</v>
+      </c>
+      <c r="B76"/>
+      <c r="C76" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="79">
@@ -3894,34 +3986,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="s">
+    <row r="81">
+      <c r="A81" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B80" t="n">
-        <v>7950</v>
-      </c>
-      <c r="C80" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>56</v>
-      </c>
-      <c r="B81" t="n">
-        <v>788</v>
-      </c>
-      <c r="C81" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B82" t="n">
-        <v>92</v>
+        <v>7950</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
@@ -3929,10 +4004,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B83" t="n">
-        <v>1106</v>
+        <v>788</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
@@ -3940,10 +4015,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B84" t="n">
-        <v>-999</v>
+        <v>92</v>
       </c>
       <c r="C84" t="s">
         <v>8</v>
@@ -3951,10 +4026,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B85" t="n">
-        <v>-89</v>
+        <v>1106</v>
       </c>
       <c r="C85" t="s">
         <v>8</v>
@@ -3962,41 +4037,45 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>60</v>
+      </c>
+      <c r="B86" t="n">
+        <v>-999</v>
+      </c>
+      <c r="C86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
         <v>61</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B87" t="n">
+        <v>-89</v>
+      </c>
+      <c r="C87" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>62</v>
+      </c>
+      <c r="B88" t="n">
         <v>8848</v>
       </c>
-      <c r="C86" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
+      <c r="C88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B89"/>
-      <c r="C89" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>64</v>
-      </c>
-      <c r="B90"/>
-      <c r="C90" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B91"/>
       <c r="C91" t="s">
@@ -4005,39 +4084,39 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B92"/>
       <c r="C92" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>66</v>
+      </c>
+      <c r="B93"/>
+      <c r="C93" t="s">
+        <v>8</v>
+      </c>
+    </row>
     <row r="94">
-      <c r="A94" s="2" t="s">
+      <c r="A94" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>63</v>
-      </c>
-      <c r="B95"/>
-      <c r="C95" t="s">
+      <c r="B94"/>
+      <c r="C94" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s">
-        <v>64</v>
-      </c>
-      <c r="B96"/>
-      <c r="C96" t="s">
-        <v>8</v>
+      <c r="A96" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B97"/>
       <c r="C97" t="s">
@@ -4046,46 +4125,42 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B98"/>
       <c r="C98" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>66</v>
+      </c>
+      <c r="B99"/>
+      <c r="C99" t="s">
+        <v>8</v>
+      </c>
+    </row>
     <row r="100">
-      <c r="A100" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
+      <c r="A100" t="s">
+        <v>67</v>
+      </c>
+      <c r="B100"/>
+      <c r="C100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B101" t="n">
-        <v>893</v>
-      </c>
-      <c r="C101" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>70</v>
-      </c>
-      <c r="B102" t="n">
-        <v>2621</v>
-      </c>
-      <c r="C102" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B103" t="n">
-        <v>2023</v>
+        <v>893</v>
       </c>
       <c r="C103" t="s">
         <v>8</v>
@@ -4093,10 +4168,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B104" t="n">
-        <v>3311</v>
+        <v>2621</v>
       </c>
       <c r="C104" t="s">
         <v>8</v>
@@ -4104,48 +4179,48 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
+        <v>72</v>
+      </c>
+      <c r="B105" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
         <v>73</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B106" t="n">
+        <v>3311</v>
+      </c>
+      <c r="C106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>74</v>
+      </c>
+      <c r="B107" t="n">
         <v>8848</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C107" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>55</v>
-      </c>
-      <c r="B109" t="n">
-        <v>1289</v>
-      </c>
-      <c r="C109" t="s">
-        <v>8</v>
-      </c>
-    </row>
     <row r="110">
-      <c r="A110" t="s">
-        <v>56</v>
-      </c>
-      <c r="B110" t="n">
-        <v>83</v>
-      </c>
-      <c r="C110" t="s">
-        <v>8</v>
+      <c r="A110" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B111" t="n">
-        <v>-119</v>
+        <v>1289</v>
       </c>
       <c r="C111" t="s">
         <v>8</v>
@@ -4153,10 +4228,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B112" t="n">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="C112" t="s">
         <v>8</v>
@@ -4164,10 +4239,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="B113" t="n">
-        <v>-9</v>
+        <v>-119</v>
       </c>
       <c r="C113" t="s">
         <v>8</v>
@@ -4175,10 +4250,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B114" t="n">
-        <v>-1</v>
+        <v>137</v>
       </c>
       <c r="C114" t="s">
         <v>8</v>
@@ -4186,10 +4261,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B115" t="n">
-        <v>-142</v>
+        <v>-9</v>
       </c>
       <c r="C115" t="s">
         <v>8</v>
@@ -4197,10 +4272,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B116" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="C116" t="s">
         <v>8</v>
@@ -4208,12 +4283,23 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
+        <v>79</v>
+      </c>
+      <c r="B117" t="n">
+        <v>-142</v>
+      </c>
+      <c r="C117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
         <v>80</v>
       </c>
-      <c r="B117" t="n">
-        <v>1205</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="B118" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C118" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4222,26 +4308,15 @@
         <v>81</v>
       </c>
       <c r="B119" t="n">
-        <v>40</v>
+        <v>1205</v>
       </c>
       <c r="C119" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>82</v>
-      </c>
-      <c r="B120" t="n">
-        <v>101</v>
-      </c>
-      <c r="C120" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B121"/>
       <c r="C121" t="s">
@@ -4250,88 +4325,95 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B122"/>
       <c r="C122" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="s">
+    <row r="123">
+      <c r="A123" t="s">
+        <v>84</v>
+      </c>
+      <c r="B123"/>
+      <c r="C123" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
+      <c r="B124"/>
+      <c r="C124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B126" t="n">
-        <v>274</v>
-      </c>
-      <c r="C126" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>87</v>
-      </c>
-      <c r="B127" t="n">
-        <v>39</v>
-      </c>
-      <c r="C127" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>88</v>
-      </c>
-      <c r="B128"/>
+        <v>87</v>
+      </c>
+      <c r="B128" t="n">
+        <v>274</v>
+      </c>
       <c r="C128" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>89</v>
-      </c>
-      <c r="B129"/>
+        <v>88</v>
+      </c>
+      <c r="B129" t="n">
+        <v>39</v>
+      </c>
       <c r="C129" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>90</v>
-      </c>
-      <c r="B130" t="n">
-        <v>3</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B130"/>
       <c r="C130" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>91</v>
-      </c>
-      <c r="B131" t="n">
-        <v>-3</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="B131"/>
       <c r="C131" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
+        <v>91</v>
+      </c>
+      <c r="B132" t="n">
+        <v>3</v>
+      </c>
+      <c r="C132" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
         <v>92</v>
       </c>
-      <c r="B132" t="n">
-        <v>313</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="B133" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C133" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4340,26 +4422,15 @@
         <v>93</v>
       </c>
       <c r="B134" t="n">
-        <v>2</v>
+        <v>313</v>
       </c>
       <c r="C134" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>94</v>
-      </c>
-      <c r="B135" t="n">
-        <v>4</v>
-      </c>
-      <c r="C135" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B136"/>
       <c r="C136" t="s">
@@ -4368,7 +4439,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B137"/>
       <c r="C137" t="s">
@@ -4377,7 +4448,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B138"/>
       <c r="C138" t="s">
@@ -4386,241 +4457,261 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B139"/>
       <c r="C139" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="s">
+    <row r="140">
+      <c r="A140" t="s">
+        <v>98</v>
+      </c>
+      <c r="B140"/>
+      <c r="C140" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
         <v>99</v>
       </c>
+      <c r="B141"/>
+      <c r="C141" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" t="s">
+      <c r="A144" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="B144" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C144" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>102</v>
-      </c>
-      <c r="B145"/>
-      <c r="C145" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>103</v>
-      </c>
-      <c r="B146"/>
+        <v>101</v>
+      </c>
+      <c r="B146" t="n">
+        <v>2.2</v>
+      </c>
       <c r="C146" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B147"/>
       <c r="C147" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
+        <v>104</v>
+      </c>
+      <c r="B148"/>
+      <c r="C148" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
         <v>105</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B149"/>
+      <c r="C149" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>106</v>
+      </c>
+      <c r="B150" t="n">
         <v>2089</v>
       </c>
-      <c r="C148" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="s">
-        <v>106</v>
+      <c r="C150" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="s">
+      <c r="A153" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="B153"/>
-      <c r="C153" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>109</v>
-      </c>
-      <c r="B154"/>
-      <c r="C154" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B155"/>
       <c r="C155" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>111</v>
-      </c>
-      <c r="B156" t="n">
-        <v>22374</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B156"/>
       <c r="C156" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B157"/>
       <c r="C157" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>113</v>
-      </c>
-      <c r="B158"/>
+        <v>112</v>
+      </c>
+      <c r="B158" t="n">
+        <v>22374</v>
+      </c>
       <c r="C158" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="B159"/>
       <c r="C159" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="B160"/>
       <c r="C160" t="s">
-        <v>12</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>92</v>
+      </c>
+      <c r="B161" t="n">
+        <v>2234</v>
+      </c>
+      <c r="C161" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>114</v>
-      </c>
-      <c r="B162" t="n">
-        <v>99469</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B162"/>
       <c r="C162" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>115</v>
-      </c>
-      <c r="B163" t="n">
-        <v>56570</v>
-      </c>
-      <c r="C163" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
+        <v>115</v>
+      </c>
+      <c r="B164" t="n">
+        <v>99469</v>
+      </c>
+      <c r="C164" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
         <v>116</v>
       </c>
-      <c r="B164" t="n">
+      <c r="B165" t="n">
+        <v>56570</v>
+      </c>
+      <c r="C165" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>117</v>
+      </c>
+      <c r="B166" t="n">
         <v>22374</v>
       </c>
-      <c r="C164" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="s">
-        <v>117</v>
+      <c r="C166" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="s">
+      <c r="A169" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B169" t="n">
-        <v>8787</v>
-      </c>
-      <c r="C169" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>120</v>
-      </c>
-      <c r="B170"/>
-      <c r="C170" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B171" t="n">
-        <v>4469</v>
+        <v>8787</v>
       </c>
       <c r="C171" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B172"/>
       <c r="C172" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>123</v>
-      </c>
-      <c r="B173"/>
+        <v>122</v>
+      </c>
+      <c r="B173" t="n">
+        <v>4469</v>
+      </c>
       <c r="C173" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
+        <v>123</v>
+      </c>
+      <c r="B174"/>
+      <c r="C174" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>124</v>
+      </c>
+      <c r="B175"/>
+      <c r="C175" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
         <v>18</v>
       </c>
-      <c r="B174" t="n">
+      <c r="B176" t="n">
         <v>13256</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C176" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4642,7 +4733,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2">
@@ -4652,7 +4743,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -4675,9 +4766,7 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="n">
-        <v>29255</v>
-      </c>
+      <c r="B7"/>
       <c r="C7" t="s">
         <v>8</v>
       </c>
@@ -4686,9 +4775,7 @@
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="n">
-        <v>14132</v>
-      </c>
+      <c r="B8"/>
       <c r="C8" t="s">
         <v>8</v>
       </c>
@@ -4706,9 +4793,7 @@
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="n">
-        <v>43387</v>
-      </c>
+      <c r="B10"/>
       <c r="C10" t="s">
         <v>12</v>
       </c>
@@ -5011,23 +5096,23 @@
         <v>37</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="s">
+    <row r="58">
+      <c r="A58" t="s">
         <v>44</v>
       </c>
+      <c r="B58"/>
+      <c r="C58" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60"/>
-      <c r="C60" t="s">
-        <v>37</v>
+      <c r="A60" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B61"/>
       <c r="C61" t="s">
@@ -5036,7 +5121,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B62"/>
       <c r="C62" t="s">
@@ -5045,7 +5130,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B63"/>
       <c r="C63" t="s">
@@ -5054,7 +5139,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B64"/>
       <c r="C64" t="s">
@@ -5063,7 +5148,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B65"/>
       <c r="C65" t="s">
@@ -5072,81 +5157,94 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B66"/>
       <c r="C66" t="s">
         <v>37</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>43</v>
+      </c>
+      <c r="B67"/>
+      <c r="C67" t="s">
+        <v>37</v>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68"/>
+      <c r="C68" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B69" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="C69" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>47</v>
-      </c>
-      <c r="B70" t="n">
-        <v>20</v>
-      </c>
-      <c r="C70" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B71" t="n">
-        <v>0.04</v>
+        <v>0.033</v>
       </c>
       <c r="C71" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>50</v>
-      </c>
-      <c r="B72"/>
+        <v>48</v>
+      </c>
+      <c r="B72" t="n">
+        <v>20</v>
+      </c>
       <c r="C72" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>51</v>
-      </c>
-      <c r="B73"/>
+        <v>49</v>
+      </c>
+      <c r="B73" t="n">
+        <v>0.04</v>
+      </c>
       <c r="C73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B74"/>
       <c r="C74" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>52</v>
+      </c>
+      <c r="B75"/>
+      <c r="C75" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
         <v>53</v>
+      </c>
+      <c r="B76"/>
+      <c r="C76" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="79">
@@ -5154,34 +5252,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="s">
+    <row r="81">
+      <c r="A81" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B80" t="n">
-        <v>1994</v>
-      </c>
-      <c r="C80" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>56</v>
-      </c>
-      <c r="B81" t="n">
-        <v>195</v>
-      </c>
-      <c r="C81" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B82" t="n">
-        <v>25</v>
+        <v>1994</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
@@ -5189,10 +5270,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B83" t="n">
-        <v>629</v>
+        <v>195</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
@@ -5200,10 +5281,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B84" t="n">
-        <v>-197</v>
+        <v>25</v>
       </c>
       <c r="C84" t="s">
         <v>8</v>
@@ -5211,50 +5292,54 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>60</v>
-      </c>
-      <c r="B85"/>
+        <v>59</v>
+      </c>
+      <c r="B85" t="n">
+        <v>629</v>
+      </c>
       <c r="C85" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>60</v>
+      </c>
+      <c r="B86" t="n">
+        <v>-197</v>
+      </c>
+      <c r="C86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
         <v>61</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B87"/>
+      <c r="C87" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>62</v>
+      </c>
+      <c r="B88" t="n">
         <v>2645</v>
       </c>
-      <c r="C86" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
+      <c r="C88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B89"/>
-      <c r="C89" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>64</v>
-      </c>
-      <c r="B90"/>
-      <c r="C90" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B91"/>
       <c r="C91" t="s">
@@ -5263,39 +5348,39 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B92"/>
       <c r="C92" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>66</v>
+      </c>
+      <c r="B93"/>
+      <c r="C93" t="s">
+        <v>8</v>
+      </c>
+    </row>
     <row r="94">
-      <c r="A94" s="2" t="s">
+      <c r="A94" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>63</v>
-      </c>
-      <c r="B95"/>
-      <c r="C95" t="s">
+      <c r="B94"/>
+      <c r="C94" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s">
-        <v>64</v>
-      </c>
-      <c r="B96"/>
-      <c r="C96" t="s">
-        <v>8</v>
+      <c r="A96" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B97"/>
       <c r="C97" t="s">
@@ -5304,46 +5389,42 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B98"/>
       <c r="C98" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>66</v>
+      </c>
+      <c r="B99"/>
+      <c r="C99" t="s">
+        <v>8</v>
+      </c>
+    </row>
     <row r="100">
-      <c r="A100" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
+      <c r="A100" t="s">
+        <v>67</v>
+      </c>
+      <c r="B100"/>
+      <c r="C100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B101" t="n">
-        <v>165</v>
-      </c>
-      <c r="C101" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>70</v>
-      </c>
-      <c r="B102" t="n">
-        <v>562</v>
-      </c>
-      <c r="C102" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B103" t="n">
-        <v>539</v>
+        <v>165</v>
       </c>
       <c r="C103" t="s">
         <v>8</v>
@@ -5351,10 +5432,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B104" t="n">
-        <v>1380</v>
+        <v>562</v>
       </c>
       <c r="C104" t="s">
         <v>8</v>
@@ -5362,48 +5443,48 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
+        <v>72</v>
+      </c>
+      <c r="B105" t="n">
+        <v>539</v>
+      </c>
+      <c r="C105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
         <v>73</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B106" t="n">
+        <v>1380</v>
+      </c>
+      <c r="C106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>74</v>
+      </c>
+      <c r="B107" t="n">
         <v>2645</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C107" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>55</v>
-      </c>
-      <c r="B109" t="n">
-        <v>942</v>
-      </c>
-      <c r="C109" t="s">
-        <v>8</v>
-      </c>
-    </row>
     <row r="110">
-      <c r="A110" t="s">
-        <v>56</v>
-      </c>
-      <c r="B110" t="n">
-        <v>67</v>
-      </c>
-      <c r="C110" t="s">
-        <v>8</v>
+      <c r="A110" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>942</v>
       </c>
       <c r="C111" t="s">
         <v>8</v>
@@ -5411,10 +5492,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B112" t="n">
-        <v>-220</v>
+        <v>67</v>
       </c>
       <c r="C112" t="s">
         <v>8</v>
@@ -5422,21 +5503,19 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>76</v>
-      </c>
-      <c r="B113" t="n">
-        <v>-7</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B113"/>
       <c r="C113" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>-220</v>
       </c>
       <c r="C114" t="s">
         <v>8</v>
@@ -5444,10 +5523,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B115" t="n">
-        <v>-36</v>
+        <v>-7</v>
       </c>
       <c r="C115" t="s">
         <v>8</v>
@@ -5455,7 +5534,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B116"/>
       <c r="C116" t="s">
@@ -5464,12 +5543,21 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
+        <v>79</v>
+      </c>
+      <c r="B117" t="n">
+        <v>-36</v>
+      </c>
+      <c r="C117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
         <v>80</v>
       </c>
-      <c r="B117" t="n">
-        <v>746</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="B118"/>
+      <c r="C118" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5477,23 +5565,16 @@
       <c r="A119" t="s">
         <v>81</v>
       </c>
-      <c r="B119"/>
+      <c r="B119" t="n">
+        <v>746</v>
+      </c>
       <c r="C119" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>82</v>
-      </c>
-      <c r="B120"/>
-      <c r="C120" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B121"/>
       <c r="C121" t="s">
@@ -5502,72 +5583,70 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B122"/>
       <c r="C122" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="s">
+    <row r="123">
+      <c r="A123" t="s">
+        <v>84</v>
+      </c>
+      <c r="B123"/>
+      <c r="C123" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
+      <c r="B124"/>
+      <c r="C124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B126" t="n">
-        <v>98</v>
-      </c>
-      <c r="C126" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>87</v>
-      </c>
-      <c r="B127" t="n">
-        <v>-4</v>
-      </c>
-      <c r="C127" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>88</v>
-      </c>
-      <c r="B128"/>
+        <v>87</v>
+      </c>
+      <c r="B128" t="n">
+        <v>98</v>
+      </c>
       <c r="C128" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>89</v>
-      </c>
-      <c r="B129"/>
+        <v>88</v>
+      </c>
+      <c r="B129" t="n">
+        <v>-4</v>
+      </c>
       <c r="C129" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>90</v>
-      </c>
-      <c r="B130" t="n">
-        <v>1</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B130"/>
       <c r="C130" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B131"/>
       <c r="C131" t="s">
@@ -5576,12 +5655,21 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
+        <v>91</v>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
         <v>92</v>
       </c>
-      <c r="B132" t="n">
-        <v>85</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="B133"/>
+      <c r="C133" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5589,23 +5677,16 @@
       <c r="A134" t="s">
         <v>93</v>
       </c>
-      <c r="B134"/>
+      <c r="B134" t="n">
+        <v>85</v>
+      </c>
       <c r="C134" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>94</v>
-      </c>
-      <c r="B135"/>
-      <c r="C135" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B136"/>
       <c r="C136" t="s">
@@ -5614,7 +5695,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B137"/>
       <c r="C137" t="s">
@@ -5623,7 +5704,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B138"/>
       <c r="C138" t="s">
@@ -5632,247 +5713,253 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B139"/>
       <c r="C139" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="s">
+    <row r="140">
+      <c r="A140" t="s">
+        <v>98</v>
+      </c>
+      <c r="B140"/>
+      <c r="C140" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
         <v>99</v>
       </c>
+      <c r="B141"/>
+      <c r="C141" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" t="s">
+      <c r="A144" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="B144" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="C144" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>102</v>
-      </c>
-      <c r="B145"/>
-      <c r="C145" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B146" t="n">
-        <v>1790</v>
+        <v>1.97</v>
       </c>
       <c r="C146" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>104</v>
-      </c>
-      <c r="B147" t="n">
-        <v>3532</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B147"/>
       <c r="C147" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
+        <v>104</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1790</v>
+      </c>
+      <c r="C148" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
         <v>105</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B149" t="n">
+        <v>3532</v>
+      </c>
+      <c r="C149" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>106</v>
+      </c>
+      <c r="B150" t="n">
         <v>569</v>
       </c>
-      <c r="C148" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="s">
-        <v>106</v>
+      <c r="C150" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="s">
+      <c r="A153" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="B153" t="n">
-        <v>2254</v>
-      </c>
-      <c r="C153" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>109</v>
-      </c>
-      <c r="B154"/>
-      <c r="C154" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B155"/>
       <c r="C155" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>111</v>
-      </c>
-      <c r="B156" t="n">
-        <v>3282</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B156"/>
       <c r="C156" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>112</v>
-      </c>
-      <c r="B157" t="n">
-        <v>8440</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B157"/>
       <c r="C157" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B158" t="n">
-        <v>-3473</v>
+        <v>3282</v>
       </c>
       <c r="C158" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>91</v>
-      </c>
-      <c r="B159" t="n">
-        <v>4027</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="B159"/>
       <c r="C159" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>18</v>
-      </c>
-      <c r="B160" t="n">
-        <v>66502</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B160"/>
       <c r="C160" t="s">
-        <v>12</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>92</v>
+      </c>
+      <c r="B161"/>
+      <c r="C161" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>114</v>
+        <v>18</v>
       </c>
       <c r="B162"/>
       <c r="C162" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>115</v>
-      </c>
-      <c r="B163" t="n">
-        <v>66502</v>
-      </c>
-      <c r="C163" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B164"/>
       <c r="C164" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>116</v>
+      </c>
+      <c r="B165"/>
+      <c r="C165" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
         <v>117</v>
       </c>
+      <c r="B166"/>
+      <c r="C166" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" t="s">
+      <c r="A169" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B169"/>
-      <c r="C169" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>120</v>
-      </c>
-      <c r="B170"/>
-      <c r="C170" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B171"/>
       <c r="C171" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B172"/>
       <c r="C172" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B173"/>
       <c r="C173" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
+        <v>123</v>
+      </c>
+      <c r="B174"/>
+      <c r="C174" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>124</v>
+      </c>
+      <c r="B175"/>
+      <c r="C175" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
         <v>18</v>
       </c>
-      <c r="B174" t="n">
+      <c r="B176" t="n">
         <v>3147</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C176" t="s">
         <v>12</v>
       </c>
     </row>

--- a/All_Insurers_2025_Databook.xlsx
+++ b/All_Insurers_2025_Databook.xlsx
@@ -1954,7 +1954,7 @@
         <v>113</v>
       </c>
       <c r="B159" t="n">
-        <v>4705</v>
+        <v>5005</v>
       </c>
       <c r="C159" t="s">
         <v>109</v>
@@ -4913,7 +4913,9 @@
       <c r="A28" t="s">
         <v>19</v>
       </c>
-      <c r="B28"/>
+      <c r="B28" t="n">
+        <v>101</v>
+      </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
@@ -4938,7 +4940,9 @@
       <c r="A34" t="s">
         <v>23</v>
       </c>
-      <c r="B34"/>
+      <c r="B34" t="n">
+        <v>-197</v>
+      </c>
       <c r="C34" t="s">
         <v>24</v>
       </c>
@@ -4947,7 +4951,9 @@
       <c r="A35" t="s">
         <v>25</v>
       </c>
-      <c r="B35"/>
+      <c r="B35" t="n">
+        <v>-36</v>
+      </c>
       <c r="C35" t="s">
         <v>24</v>
       </c>
@@ -5037,7 +5043,9 @@
       <c r="A51" t="s">
         <v>36</v>
       </c>
-      <c r="B51"/>
+      <c r="B51" t="n">
+        <v>0.03</v>
+      </c>
       <c r="C51" t="s">
         <v>37</v>
       </c>
@@ -5046,7 +5054,9 @@
       <c r="A52" t="s">
         <v>38</v>
       </c>
-      <c r="B52"/>
+      <c r="B52" t="n">
+        <v>0.0343</v>
+      </c>
       <c r="C52" t="s">
         <v>37</v>
       </c>
@@ -5055,7 +5065,9 @@
       <c r="A53" t="s">
         <v>39</v>
       </c>
-      <c r="B53"/>
+      <c r="B53" t="n">
+        <v>0.0385</v>
+      </c>
       <c r="C53" t="s">
         <v>37</v>
       </c>
@@ -5064,7 +5076,9 @@
       <c r="A54" t="s">
         <v>40</v>
       </c>
-      <c r="B54"/>
+      <c r="B54" t="n">
+        <v>0.0412</v>
+      </c>
       <c r="C54" t="s">
         <v>37</v>
       </c>
@@ -5073,7 +5087,9 @@
       <c r="A55" t="s">
         <v>41</v>
       </c>
-      <c r="B55"/>
+      <c r="B55" t="n">
+        <v>0.0423</v>
+      </c>
       <c r="C55" t="s">
         <v>37</v>
       </c>
@@ -5082,7 +5098,9 @@
       <c r="A56" t="s">
         <v>42</v>
       </c>
-      <c r="B56"/>
+      <c r="B56" t="n">
+        <v>0.043</v>
+      </c>
       <c r="C56" t="s">
         <v>37</v>
       </c>
@@ -5100,7 +5118,9 @@
       <c r="A58" t="s">
         <v>44</v>
       </c>
-      <c r="B58"/>
+      <c r="B58" t="n">
+        <v>0.043</v>
+      </c>
       <c r="C58" t="s">
         <v>37</v>
       </c>
@@ -5114,7 +5134,9 @@
       <c r="A61" t="s">
         <v>36</v>
       </c>
-      <c r="B61"/>
+      <c r="B61" t="n">
+        <v>0.0322</v>
+      </c>
       <c r="C61" t="s">
         <v>37</v>
       </c>
@@ -5123,7 +5145,9 @@
       <c r="A62" t="s">
         <v>38</v>
       </c>
-      <c r="B62"/>
+      <c r="B62" t="n">
+        <v>0.0365</v>
+      </c>
       <c r="C62" t="s">
         <v>37</v>
       </c>
@@ -5132,7 +5156,9 @@
       <c r="A63" t="s">
         <v>39</v>
       </c>
-      <c r="B63"/>
+      <c r="B63" t="n">
+        <v>0.0409</v>
+      </c>
       <c r="C63" t="s">
         <v>37</v>
       </c>
@@ -5141,7 +5167,9 @@
       <c r="A64" t="s">
         <v>40</v>
       </c>
-      <c r="B64"/>
+      <c r="B64" t="n">
+        <v>0.0435</v>
+      </c>
       <c r="C64" t="s">
         <v>37</v>
       </c>
@@ -5150,7 +5178,9 @@
       <c r="A65" t="s">
         <v>41</v>
       </c>
-      <c r="B65"/>
+      <c r="B65" t="n">
+        <v>0.0446</v>
+      </c>
       <c r="C65" t="s">
         <v>37</v>
       </c>
@@ -5159,7 +5189,9 @@
       <c r="A66" t="s">
         <v>42</v>
       </c>
-      <c r="B66"/>
+      <c r="B66" t="n">
+        <v>0.0453</v>
+      </c>
       <c r="C66" t="s">
         <v>37</v>
       </c>
@@ -5177,7 +5209,9 @@
       <c r="A68" t="s">
         <v>44</v>
       </c>
-      <c r="B68"/>
+      <c r="B68" t="n">
+        <v>0.0454</v>
+      </c>
       <c r="C68" t="s">
         <v>37</v>
       </c>
@@ -5213,9 +5247,7 @@
       <c r="A73" t="s">
         <v>49</v>
       </c>
-      <c r="B73" t="n">
-        <v>0.04</v>
-      </c>
+      <c r="B73"/>
       <c r="C73" t="s">
         <v>50</v>
       </c>
@@ -5423,9 +5455,7 @@
       <c r="A103" t="s">
         <v>70</v>
       </c>
-      <c r="B103" t="n">
-        <v>165</v>
-      </c>
+      <c r="B103"/>
       <c r="C103" t="s">
         <v>8</v>
       </c>
@@ -5434,9 +5464,7 @@
       <c r="A104" t="s">
         <v>71</v>
       </c>
-      <c r="B104" t="n">
-        <v>562</v>
-      </c>
+      <c r="B104"/>
       <c r="C104" t="s">
         <v>8</v>
       </c>
@@ -5445,9 +5473,7 @@
       <c r="A105" t="s">
         <v>72</v>
       </c>
-      <c r="B105" t="n">
-        <v>539</v>
-      </c>
+      <c r="B105"/>
       <c r="C105" t="s">
         <v>8</v>
       </c>
@@ -5456,9 +5482,7 @@
       <c r="A106" t="s">
         <v>73</v>
       </c>
-      <c r="B106" t="n">
-        <v>1380</v>
-      </c>
+      <c r="B106"/>
       <c r="C106" t="s">
         <v>8</v>
       </c>
@@ -5467,9 +5491,7 @@
       <c r="A107" t="s">
         <v>74</v>
       </c>
-      <c r="B107" t="n">
-        <v>2645</v>
-      </c>
+      <c r="B107"/>
       <c r="C107" t="s">
         <v>12</v>
       </c>
@@ -5639,7 +5661,9 @@
       <c r="A130" t="s">
         <v>89</v>
       </c>
-      <c r="B130"/>
+      <c r="B130" t="n">
+        <v>-9</v>
+      </c>
       <c r="C130" t="s">
         <v>8</v>
       </c>
@@ -5789,9 +5813,7 @@
       <c r="A150" t="s">
         <v>106</v>
       </c>
-      <c r="B150" t="n">
-        <v>569</v>
-      </c>
+      <c r="B150"/>
       <c r="C150" t="s">
         <v>102</v>
       </c>

--- a/All_Insurers_2025_Databook.xlsx
+++ b/All_Insurers_2025_Databook.xlsx
@@ -1543,9 +1543,7 @@
       <c r="A105" t="s">
         <v>72</v>
       </c>
-      <c r="B105" t="n">
-        <v>306</v>
-      </c>
+      <c r="B105"/>
       <c r="C105" t="s">
         <v>8</v>
       </c>
@@ -1554,9 +1552,7 @@
       <c r="A106" t="s">
         <v>73</v>
       </c>
-      <c r="B106" t="n">
-        <v>533</v>
-      </c>
+      <c r="B106"/>
       <c r="C106" t="s">
         <v>8</v>
       </c>
@@ -1954,7 +1950,7 @@
         <v>113</v>
       </c>
       <c r="B159" t="n">
-        <v>5005</v>
+        <v>5049</v>
       </c>
       <c r="C159" t="s">
         <v>109</v>
@@ -2324,7 +2320,9 @@
       <c r="A34" t="s">
         <v>23</v>
       </c>
-      <c r="B34"/>
+      <c r="B34" t="n">
+        <v>466</v>
+      </c>
       <c r="C34" t="s">
         <v>24</v>
       </c>
@@ -2333,7 +2331,9 @@
       <c r="A35" t="s">
         <v>25</v>
       </c>
-      <c r="B35"/>
+      <c r="B35" t="n">
+        <v>191</v>
+      </c>
       <c r="C35" t="s">
         <v>24</v>
       </c>
@@ -2342,7 +2342,9 @@
       <c r="A36" t="s">
         <v>26</v>
       </c>
-      <c r="B36"/>
+      <c r="B36" t="n">
+        <v>3918</v>
+      </c>
       <c r="C36" t="s">
         <v>24</v>
       </c>
@@ -2423,7 +2425,9 @@
       <c r="A51" t="s">
         <v>36</v>
       </c>
-      <c r="B51"/>
+      <c r="B51" t="n">
+        <v>0.0207</v>
+      </c>
       <c r="C51" t="s">
         <v>37</v>
       </c>
@@ -2432,7 +2436,9 @@
       <c r="A52" t="s">
         <v>38</v>
       </c>
-      <c r="B52"/>
+      <c r="B52" t="n">
+        <v>0.0247</v>
+      </c>
       <c r="C52" t="s">
         <v>37</v>
       </c>
@@ -2441,7 +2447,9 @@
       <c r="A53" t="s">
         <v>39</v>
       </c>
-      <c r="B53"/>
+      <c r="B53" t="n">
+        <v>0.0285</v>
+      </c>
       <c r="C53" t="s">
         <v>37</v>
       </c>
@@ -2459,7 +2467,9 @@
       <c r="A55" t="s">
         <v>41</v>
       </c>
-      <c r="B55"/>
+      <c r="B55" t="n">
+        <v>0.032</v>
+      </c>
       <c r="C55" t="s">
         <v>37</v>
       </c>
@@ -2468,7 +2478,9 @@
       <c r="A56" t="s">
         <v>42</v>
       </c>
-      <c r="B56"/>
+      <c r="B56" t="n">
+        <v>0.0319</v>
+      </c>
       <c r="C56" t="s">
         <v>37</v>
       </c>
@@ -2477,7 +2489,9 @@
       <c r="A57" t="s">
         <v>43</v>
       </c>
-      <c r="B57"/>
+      <c r="B57" t="n">
+        <v>0.0318</v>
+      </c>
       <c r="C57" t="s">
         <v>37</v>
       </c>
@@ -2486,7 +2500,9 @@
       <c r="A58" t="s">
         <v>44</v>
       </c>
-      <c r="B58"/>
+      <c r="B58" t="n">
+        <v>0.0318</v>
+      </c>
       <c r="C58" t="s">
         <v>37</v>
       </c>
@@ -2500,7 +2516,9 @@
       <c r="A61" t="s">
         <v>36</v>
       </c>
-      <c r="B61"/>
+      <c r="B61" t="n">
+        <v>0.0265</v>
+      </c>
       <c r="C61" t="s">
         <v>37</v>
       </c>
@@ -2509,7 +2527,9 @@
       <c r="A62" t="s">
         <v>38</v>
       </c>
-      <c r="B62"/>
+      <c r="B62" t="n">
+        <v>0.0305</v>
+      </c>
       <c r="C62" t="s">
         <v>37</v>
       </c>
@@ -2518,7 +2538,9 @@
       <c r="A63" t="s">
         <v>39</v>
       </c>
-      <c r="B63"/>
+      <c r="B63" t="n">
+        <v>0.0343</v>
+      </c>
       <c r="C63" t="s">
         <v>37</v>
       </c>
@@ -2536,7 +2558,9 @@
       <c r="A65" t="s">
         <v>41</v>
       </c>
-      <c r="B65"/>
+      <c r="B65" t="n">
+        <v>0.0378</v>
+      </c>
       <c r="C65" t="s">
         <v>37</v>
       </c>
@@ -2545,7 +2569,9 @@
       <c r="A66" t="s">
         <v>42</v>
       </c>
-      <c r="B66"/>
+      <c r="B66" t="n">
+        <v>0.0368</v>
+      </c>
       <c r="C66" t="s">
         <v>37</v>
       </c>
@@ -2554,7 +2580,9 @@
       <c r="A67" t="s">
         <v>43</v>
       </c>
-      <c r="B67"/>
+      <c r="B67" t="n">
+        <v>0.0357</v>
+      </c>
       <c r="C67" t="s">
         <v>37</v>
       </c>
@@ -2563,7 +2591,9 @@
       <c r="A68" t="s">
         <v>44</v>
       </c>
-      <c r="B68"/>
+      <c r="B68" t="n">
+        <v>0.0349</v>
+      </c>
       <c r="C68" t="s">
         <v>37</v>
       </c>
@@ -2827,7 +2857,9 @@
       <c r="A103" t="s">
         <v>70</v>
       </c>
-      <c r="B103"/>
+      <c r="B103" t="n">
+        <v>297</v>
+      </c>
       <c r="C103" t="s">
         <v>8</v>
       </c>
@@ -2836,7 +2868,9 @@
       <c r="A104" t="s">
         <v>71</v>
       </c>
-      <c r="B104"/>
+      <c r="B104" t="n">
+        <v>933</v>
+      </c>
       <c r="C104" t="s">
         <v>8</v>
       </c>
@@ -2845,7 +2879,9 @@
       <c r="A105" t="s">
         <v>72</v>
       </c>
-      <c r="B105"/>
+      <c r="B105" t="n">
+        <v>919</v>
+      </c>
       <c r="C105" t="s">
         <v>8</v>
       </c>
@@ -2854,7 +2890,9 @@
       <c r="A106" t="s">
         <v>73</v>
       </c>
-      <c r="B106"/>
+      <c r="B106" t="n">
+        <v>2627</v>
+      </c>
       <c r="C106" t="s">
         <v>8</v>
       </c>
@@ -2863,7 +2901,9 @@
       <c r="A107" t="s">
         <v>74</v>
       </c>
-      <c r="B107"/>
+      <c r="B107" t="n">
+        <v>4774</v>
+      </c>
       <c r="C107" t="s">
         <v>12</v>
       </c>
@@ -3061,9 +3101,7 @@
       <c r="A132" t="s">
         <v>91</v>
       </c>
-      <c r="B132" t="n">
-        <v>3</v>
-      </c>
+      <c r="B132"/>
       <c r="C132" t="s">
         <v>8</v>
       </c>
@@ -3072,9 +3110,7 @@
       <c r="A133" t="s">
         <v>92</v>
       </c>
-      <c r="B133" t="n">
-        <v>6</v>
-      </c>
+      <c r="B133"/>
       <c r="C133" t="s">
         <v>8</v>
       </c>
